--- a/GameDesign/Storage/SampleData/Enum.xlsx
+++ b/GameDesign/Storage/SampleData/Enum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B0C4A5-88F2-44A6-8E8B-20EC4C6F43C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99B00DAD-80C4-421D-A42F-643724031AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16305" yWindow="16305" windowWidth="16410" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16200" yWindow="1215" windowWidth="16410" windowHeight="18315" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -91,11 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 마리수 이하 (-1 무제한)
-value2: 마리수 이상 (-1 무제한)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ECardEffectTarget</t>
   </si>
   <si>
@@ -124,6 +119,11 @@
   </si>
   <si>
     <t>value1: 0-승점 미획득, 1-승점 획득</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 마리수 이상 (-1 무제한)
+value2: 마리수 이하 (-1 무제한)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,12 +569,12 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -586,21 +586,21 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
         <v>8</v>
@@ -611,21 +611,21 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" t="s">
         <v>18</v>
-      </c>
-      <c r="B12" t="s">
-        <v>19</v>
       </c>
       <c r="C12">
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" t="s">
         <v>8</v>
@@ -636,16 +636,16 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
       </c>
       <c r="C14">
         <v>1</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/Enum.xlsx
+++ b/GameDesign/Storage/SampleData/Enum.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Git\Ttakji_lab-mobile_development_dep\Storage\SampleData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B0C4A5-88F2-44A6-8E8B-20EC4C6F43C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F4202F-0503-4852-B8F6-531F6A9EB009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16305" yWindow="16305" windowWidth="16410" windowHeight="9975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Enum" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
   <si>
     <t>enum_category</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -82,9 +82,6 @@
   </si>
   <si>
     <t>ECardCondition</t>
-  </si>
-  <si>
-    <t>None</t>
   </si>
   <si>
     <t>EnemyUnitExist</t>
@@ -109,21 +106,110 @@
     <t>ECardEffectTargetCondition</t>
   </si>
   <si>
+    <t>value1: 파워 이하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardEffectFunctionType</t>
+  </si>
+  <si>
+    <t>KillUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-승점 미획득, 1-승점 획득</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 자신 유닛 n장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damege</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Power_Up</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-이번턴, 1-지속</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Draw</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-자신, 1-상대</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gain_Mana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnDeck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 자신 덱 n장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OppentDeck</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 상대 덱 n장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OppentHand</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 자신 패 n장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 상대 패 n장</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnMana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OppentMana</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 자신 마나 n개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 상대 마나 n개</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>PowerUnderOrEqual</t>
-  </si>
-  <si>
-    <t>value1: 파워 이하</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ECardEffectFunctionType</t>
-  </si>
-  <si>
-    <t>KillUnit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value1: 0-승점 미획득, 1-승점 획득</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeckHighOrEqual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 장수 이상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -204,8 +290,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}" name="Enum" displayName="Enum" ref="A2:D14" totalsRowShown="0">
-  <autoFilter ref="A2:D14" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}" name="Enum" displayName="Enum" ref="A2:D26" totalsRowShown="0">
+  <autoFilter ref="A2:D26" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{7D624EA5-53C1-45CF-89CD-73313249E030}" name="enum_category"/>
     <tableColumn id="2" xr3:uid="{C13A8ED2-9687-4374-B368-30AE9D9327DB}" name="enum_value"/>
@@ -479,7 +565,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D14"/>
+  <dimension ref="A2:D26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
@@ -552,7 +638,7 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -563,18 +649,18 @@
         <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -586,66 +672,234 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
         <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>8</v>
+        <v>32</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C17">
+        <v>8</v>
+      </c>
+      <c r="D17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20">
+        <v>2</v>
+      </c>
+      <c r="D20" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" t="s">
+        <v>20</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23">
+        <v>2</v>
+      </c>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+      <c r="C24">
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+      <c r="B25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C25">
+        <v>4</v>
+      </c>
+      <c r="D25" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26">
+        <v>5</v>
+      </c>
+      <c r="D26" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/Enum.xlsx
+++ b/GameDesign/Storage/SampleData/Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F4202F-0503-4852-B8F6-531F6A9EB009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC32300B-E0A3-4E5E-8A69-F55E649F1F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
   <si>
     <t>enum_category</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -88,11 +88,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 마리수 이하 (-1 무제한)
-value2: 마리수 이상 (-1 무제한)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ECardEffectTarget</t>
   </si>
   <si>
@@ -129,10 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Damege</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Power_Up</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -145,10 +136,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 0-자신, 1-상대</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Gain_Mana</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -157,18 +144,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 자신 덱 n장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OppentDeck</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 상대 덱 n장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OwnHand</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,14 +156,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 자신 패 n장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value1: 상대 패 n장</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>OwnMana</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -193,14 +164,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 자신 마나 n개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>value1: 상대 마나 n개</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>PowerUnderOrEqual</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -210,6 +173,29 @@
   </si>
   <si>
     <t>value1: 장수 이상</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 마리수 이상 (-1 무제한)
+value2: 마리수 이하 (-1 무제한)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 매수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-이번턴, 1-지속
+value2: 수량</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamegeToUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-승점 미획득, 1-승점 획득
+value2: 주는 데미지</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -655,12 +641,12 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>13</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
         <v>8</v>
@@ -672,119 +658,101 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
       </c>
       <c r="C10">
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
-      <c r="D13" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C14">
         <v>5</v>
       </c>
-      <c r="D14" t="s">
-        <v>36</v>
-      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C15">
         <v>6</v>
       </c>
-      <c r="D15" t="s">
-        <v>37</v>
-      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>7</v>
       </c>
-      <c r="D16" t="s">
-        <v>40</v>
-      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C17">
         <v>8</v>
       </c>
-      <c r="D17" t="s">
-        <v>41</v>
-      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" t="s">
         <v>8</v>
@@ -795,35 +763,35 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
       <c r="D19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
         <v>8</v>
@@ -832,74 +800,74 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
         <v>19</v>
-      </c>
-      <c r="B22" t="s">
-        <v>20</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
-      <c r="D22" t="s">
-        <v>21</v>
+      <c r="D22" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>2</v>
       </c>
       <c r="D23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>18</v>
+      </c>
+      <c r="B25" t="s">
         <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" t="s">
-        <v>29</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
-      <c r="D25" t="s">
-        <v>26</v>
+      <c r="D25" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/Enum.xlsx
+++ b/GameDesign/Storage/SampleData/Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC32300B-E0A3-4E5E-8A69-F55E649F1F74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D581D7F2-A4E5-4236-8014-D5A9BAF47087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,10 +128,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>value1: 0-이번턴, 1-지속</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Draw</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -196,6 +192,11 @@
   <si>
     <t>value1: 0-승점 미획득, 1-승점 획득
 value2: 주는 데미지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value1: 0-이번턴, 1-지속
+value2 : 증감값</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -641,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -689,7 +690,7 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -700,7 +701,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -711,7 +712,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -722,7 +723,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -733,7 +734,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16">
         <v>7</v>
@@ -744,7 +745,7 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C17">
         <v>8</v>
@@ -766,7 +767,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -780,13 +781,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -811,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -819,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -828,7 +829,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -838,8 +839,8 @@
       <c r="C24">
         <v>3</v>
       </c>
-      <c r="D24" t="s">
-        <v>24</v>
+      <c r="D24" s="2" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -847,13 +848,13 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -861,13 +862,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/Enum.xlsx
+++ b/GameDesign/Storage/SampleData/Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D581D7F2-A4E5-4236-8014-D5A9BAF47087}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25131FA-A254-4DCC-ADA1-FE7170C76B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -164,10 +164,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DeckHighOrEqual</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>value1: 장수 이상</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -186,10 +182,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>DamegeToUnit</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>value1: 0-승점 미획득, 1-승점 획득
 value2: 주는 데미지</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,6 +189,14 @@
   <si>
     <t>value1: 0-이번턴, 1-지속
 value2 : 증감값</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DamageToUnit</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeckMoreOrEqual</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -642,7 +642,7 @@
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
@@ -781,13 +781,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -820,7 +820,7 @@
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C23">
         <v>2</v>
@@ -840,7 +840,7 @@
         <v>3</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -854,7 +854,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -868,7 +868,7 @@
         <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/GameDesign/Storage/SampleData/Enum.xlsx
+++ b/GameDesign/Storage/SampleData/Enum.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wnsal\Ttakji_lab-mobile_development_dep\GameDesign\Storage\SampleData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25131FA-A254-4DCC-ADA1-FE7170C76B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E17791-EDEE-4F2A-AFA9-20E3EBDD080C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="43">
   <si>
     <t>enum_category</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -197,6 +197,14 @@
   </si>
   <si>
     <t>DeckMoreOrEqual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>OwnUnitExist</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ECardCondition</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -277,8 +285,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}" name="Enum" displayName="Enum" ref="A2:D26" totalsRowShown="0">
-  <autoFilter ref="A2:D26" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}" name="Enum" displayName="Enum" ref="A2:D27" totalsRowShown="0">
+  <autoFilter ref="A2:D27" xr:uid="{BC780932-CA1A-48F4-A036-BFD57D13E0E9}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{7D624EA5-53C1-45CF-89CD-73313249E030}" name="enum_category"/>
     <tableColumn id="2" xr3:uid="{C13A8ED2-9687-4374-B368-30AE9D9327DB}" name="enum_value"/>
@@ -552,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:D26"/>
+  <dimension ref="A2:D27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.75" bestFit="1" customWidth="1"/>
@@ -645,44 +653,44 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="D10" s="2"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -690,10 +698,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C12">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
@@ -701,10 +712,10 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
@@ -712,10 +723,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
@@ -723,10 +734,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
@@ -734,10 +745,10 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -745,21 +756,21 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18">
         <v>8</v>
-      </c>
-      <c r="C18">
-        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -767,13 +778,10 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -781,66 +789,66 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="C21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C23">
-        <v>2</v>
-      </c>
-      <c r="D23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="33" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>38</v>
+        <v>2</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="33" x14ac:dyDescent="0.3">
@@ -848,26 +856,40 @@
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="33" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="B26" t="s">
+        <v>25</v>
+      </c>
+      <c r="C26">
+        <v>4</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B27" t="s">
         <v>24</v>
       </c>
-      <c r="C26">
+      <c r="C27">
         <v>5</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>35</v>
       </c>
     </row>
